--- a/excel_inputs_files/turblatter/turblatter_zeitlos.xlsx
+++ b/excel_inputs_files/turblatter/turblatter_zeitlos.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Coding Projects\Automated Quotations\excel_inputs_files\turblatter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DD0CE0-B209-4062-B0DB-0789AC4BADCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEC1B4B-7395-467F-A348-9D6C85352ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="3" xr2:uid="{BD9F7D6E-9E12-42DC-B68D-5470724322E4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{BD9F7D6E-9E12-42DC-B68D-5470724322E4}"/>
   </bookViews>
   <sheets>
     <sheet name="1985_2110_code" sheetId="1" r:id="rId1"/>
     <sheet name="2235_code" sheetId="2" r:id="rId2"/>
-    <sheet name="Zwischenmaße(-1985_-2110)_code" sheetId="3" r:id="rId3"/>
-    <sheet name="Sondermaße(-1985_-2110)_code" sheetId="4" r:id="rId4"/>
-    <sheet name="Sondermaße(original)" sheetId="6" r:id="rId5"/>
-    <sheet name="Zwischenmaße(original)" sheetId="5" r:id="rId6"/>
+    <sheet name="Zwischenmabe(-1985_-2110)_code" sheetId="3" r:id="rId3"/>
+    <sheet name="Sondermabe(-1985_-2110)_code" sheetId="4" r:id="rId4"/>
+    <sheet name="Sondermabe(original)" sheetId="6" r:id="rId5"/>
+    <sheet name="Zwischenmabe(original)" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
